--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
@@ -446,7 +446,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Organization.extension:prefectureNo</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2762" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -679,7 +679,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -839,10 +839,6 @@
     <t>Organization.identifier:medicalInstitutionCode.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>Organization.identifier:insurerNumber</t>
   </si>
   <si>
@@ -948,7 +944,7 @@
     <t>組織を分類するために使用されます。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1580,7 +1576,7 @@
     <t>「連絡を取りたい目的のための連絡先」となります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>./type</t>
@@ -1647,7 +1643,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1964,17 +1960,17 @@
   <dimension ref="A1:AN75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.2421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.09765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.0703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="91.34375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1983,26 +1979,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.72265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5469,7 +5465,7 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>240</v>
@@ -5557,13 +5553,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -5588,13 +5584,13 @@
         <v>168</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>252</v>
@@ -5675,7 +5671,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>179</v>
@@ -5787,7 +5783,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>185</v>
@@ -5901,7 +5897,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>191</v>
@@ -6017,7 +6013,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>202</v>
@@ -6133,7 +6129,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>213</v>
@@ -6178,7 +6174,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6249,7 +6245,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>222</v>
@@ -6284,7 +6280,7 @@
         <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6363,7 +6359,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>230</v>
@@ -6475,7 +6471,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>238</v>
@@ -6501,7 +6497,7 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>240</v>
@@ -6589,10 +6585,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6615,26 +6611,26 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="O41" t="s" s="2">
+      <c r="P41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q41" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="P41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="R41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6678,7 +6674,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6693,24 +6689,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>288</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6736,16 +6732,16 @@
         <v>203</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6770,14 +6766,14 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6794,7 +6790,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6809,24 +6805,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>184</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6852,16 +6848,16 @@
         <v>180</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6910,7 +6906,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6925,13 +6921,13 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -6939,10 +6935,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6968,16 +6964,16 @@
         <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7026,7 +7022,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7044,7 +7040,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7055,10 +7051,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7081,19 +7077,19 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7142,7 +7138,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7151,19 +7147,19 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AJ45" t="s" s="2">
+      <c r="AK45" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AK45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7171,10 +7167,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7200,10 +7196,10 @@
         <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7283,10 +7279,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7312,10 +7308,10 @@
         <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>164</v>
@@ -7359,7 +7355,7 @@
         <v>136</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7397,10 +7393,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7426,13 +7422,13 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7461,28 +7457,28 @@
         <v>196</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7491,19 +7487,19 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7511,10 +7507,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7540,16 +7536,16 @@
         <v>180</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -7598,7 +7594,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7613,10 +7609,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>229</v>
@@ -7627,10 +7623,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7656,16 +7652,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7693,28 +7689,28 @@
         <v>196</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7729,13 +7725,13 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7743,10 +7739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7769,16 +7765,16 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7828,7 +7824,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7857,10 +7853,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7886,13 +7882,13 @@
         <v>231</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7942,7 +7938,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7960,7 +7956,7 @@
         <v>131</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>237</v>
@@ -7971,10 +7967,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7997,19 +7993,19 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8058,7 +8054,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8067,19 +8063,19 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AJ53" t="s" s="2">
+      <c r="AK53" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AK53" t="s" s="2">
+      <c r="AL53" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8087,10 +8083,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8199,10 +8195,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8313,10 +8309,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8342,16 +8338,16 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8379,28 +8375,28 @@
         <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z56" t="s" s="2">
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8415,13 +8411,13 @@
         <v>200</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8429,10 +8425,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8458,13 +8454,13 @@
         <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8493,28 +8489,28 @@
         <v>196</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8529,10 +8525,10 @@
         <v>200</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8543,10 +8539,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8572,16 +8568,16 @@
         <v>180</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8630,7 +8626,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8645,10 +8641,10 @@
         <v>200</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8659,10 +8655,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8688,13 +8684,13 @@
         <v>180</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8744,7 +8740,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8759,13 +8755,13 @@
         <v>200</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8773,14 +8769,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8802,13 +8798,13 @@
         <v>180</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8858,7 +8854,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8873,13 +8869,13 @@
         <v>200</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8887,14 +8883,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8916,13 +8912,13 @@
         <v>180</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8972,7 +8968,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8987,10 +8983,10 @@
         <v>200</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9001,14 +8997,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9030,13 +9026,13 @@
         <v>180</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9086,7 +9082,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9101,13 +9097,13 @@
         <v>200</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9115,14 +9111,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9144,13 +9140,13 @@
         <v>180</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9200,7 +9196,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9215,13 +9211,13 @@
         <v>200</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9229,10 +9225,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9258,13 +9254,13 @@
         <v>180</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9314,7 +9310,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9329,13 +9325,13 @@
         <v>200</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9343,10 +9339,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9372,16 +9368,16 @@
         <v>231</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9430,7 +9426,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9445,10 +9441,10 @@
         <v>200</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>237</v>
@@ -9459,10 +9455,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9488,16 +9484,16 @@
         <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9546,7 +9542,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9561,10 +9557,10 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>184</v>
@@ -9575,10 +9571,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9601,19 +9597,19 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -9662,7 +9658,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9680,7 +9676,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9691,10 +9687,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9720,10 +9716,10 @@
         <v>180</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9803,10 +9799,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9832,10 +9828,10 @@
         <v>133</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>164</v>
@@ -9917,14 +9913,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9946,10 +9942,10 @@
         <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>164</v>
@@ -10004,7 +10000,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10033,10 +10029,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10062,14 +10058,14 @@
         <v>203</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10097,11 +10093,11 @@
         <v>208</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10118,7 +10114,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10136,7 +10132,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10147,10 +10143,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10173,17 +10169,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10232,7 +10228,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10247,10 +10243,10 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10261,10 +10257,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10287,17 +10283,17 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10346,7 +10342,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10361,10 +10357,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10375,10 +10371,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10401,17 +10397,17 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10460,7 +10456,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10475,10 +10471,10 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10489,10 +10485,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10515,19 +10511,19 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10576,7 +10572,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-organization.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
